--- a/api/templates/device_activity/fr.xlsx
+++ b/api/templates/device_activity/fr.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7598CC9F-CB45-3542-954E-27BF46B20BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Activity Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Detailed by assay" state="visible" r:id="rId5"/>
+    <sheet name="Résumé des activités" sheetId="1" r:id="rId1"/>
+    <sheet name="Détails par Essai" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Activité de l’appareil</t>
   </si>
@@ -80,61 +81,54 @@
     <t>LGA: &lt;Lgas&gt;</t>
   </si>
   <si>
-    <t>Device</t>
-  </si>
-  <si>
-    <t>Assay</t>
-  </si>
-  <si>
-    <t>Last Result Update</t>
-  </si>
-  <si>
-    <t>Maintenance status</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>&lt;assayName&gt;</t>
+  </si>
+  <si>
+    <t>Essai</t>
+  </si>
+  <si>
+    <t>Statut de maintenance</t>
+  </si>
+  <si>
+    <t>Numéro de série</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -151,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -160,10 +154,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="slantDashDot">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -177,9 +192,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,501 +508,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="5" max="5" width="29.5" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="4" width="26.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="29.5" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G113"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G114"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="38.6640625" customWidth="1"/>
-    <col min="4" max="4" width="37.1640625" customWidth="1"/>
-    <col min="5" max="5" width="36.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="4" width="26.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="29.5" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E26" s="6"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E42" s="6"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E54" s="6"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E55" s="6"/>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E56" s="6"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E57" s="6"/>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E58" s="6"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E59" s="6"/>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E60" s="6"/>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E61" s="6"/>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E62" s="6"/>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E63" s="6"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E64" s="6"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E65" s="6"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E66" s="6"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E67" s="6"/>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E68" s="6"/>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E69" s="6"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E70" s="6"/>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E71" s="6"/>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E72" s="6"/>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E73" s="6"/>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E74" s="6"/>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E75" s="6"/>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E76" s="6"/>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E77" s="6"/>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E78" s="6"/>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E79" s="6"/>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E80" s="6"/>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E81" s="6"/>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E82" s="6"/>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E83" s="6"/>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E84" s="6"/>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E85" s="6"/>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E86" s="6"/>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E87" s="6"/>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E88" s="6"/>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E89" s="6"/>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E90" s="6"/>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E91" s="6"/>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E92" s="6"/>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E93" s="6"/>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E94" s="6"/>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E95" s="6"/>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E96" s="6"/>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E97" s="6"/>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E98" s="6"/>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E99" s="6"/>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E100" s="6"/>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E101" s="6"/>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E102" s="6"/>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E103" s="6"/>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E104" s="6"/>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E105" s="6"/>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E106" s="6"/>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E107" s="6"/>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E108" s="6"/>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E109" s="6"/>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E110" s="6"/>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E111" s="6"/>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E112" s="6"/>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E113" s="6"/>
-    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/fr.xlsx
+++ b/api/templates/device_activity/fr.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7598CC9F-CB45-3542-954E-27BF46B20BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="Résumé des activités" sheetId="1" r:id="rId1"/>
-    <sheet name="Détails par Essai" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Résumé des activités" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Détails par Essai" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Activité de l’appareil</t>
   </si>
@@ -33,13 +32,19 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Appareil</t>
   </si>
   <si>
-    <t>Site</t>
+    <t>Essai</t>
   </si>
   <si>
     <t>Serial</t>
@@ -54,10 +59,13 @@
     <t>Statut</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>&lt;siteName&gt;</t>
+    <t>&lt;assayName&gt;</t>
   </si>
   <si>
     <t>&lt;serial&gt;</t>
@@ -81,54 +89,48 @@
     <t>LGA: &lt;Lgas&gt;</t>
   </si>
   <si>
-    <t>&lt;assayName&gt;</t>
-  </si>
-  <si>
-    <t>Essai</t>
+    <t>Numéro de série</t>
   </si>
   <si>
     <t>Statut de maintenance</t>
-  </si>
-  <si>
-    <t>Numéro de série</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -154,18 +156,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="slantDashDot">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="slantDashDot"/>
       <diagonal/>
     </border>
     <border>
@@ -508,9 +502,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -520,95 +514,100 @@
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -618,190 +617,195 @@
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/fr.xlsx
+++ b/api/templates/device_activity/fr.xlsx
@@ -182,9 +182,7 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>

--- a/api/templates/device_activity/fr.xlsx
+++ b/api/templates/device_activity/fr.xlsx
@@ -32,7 +32,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -182,7 +182,7 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
